--- a/college-posters/data/字段表_211第一批.xlsx
+++ b/college-posters/data/字段表_211第一批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -703,17 +703,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>孙聪等候选人学籍未核到可靠来源，海报暂显示“校友信息核实中”</t>
+          <t>明故宫校区：明故宫遗址旁老校区；将军路校区：江宁主校区；航空航天馆：展示各型飞机</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待补（等用户提供或核实后补）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -725,39 +725,39 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>明故宫校区：明故宫遗址旁老校区；将军路校区：江宁主校区；航空航天馆：展示各型飞机</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>南京航空航天大学</t>
+          <t>西安电子科技大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>通信工程、电子信息工程、网络空间安全、集成电路设计与集成系统、计算机科学与技术、人工智能</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -769,17 +769,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>通信工程、电子信息工程、网络空间安全、集成电路设计与集成系统、计算机科学与技术、人工智能</t>
+          <t>电子信息与通信、集成电路与芯片、网络安全与互联网</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -791,17 +791,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>电子信息与通信、集成电路与芯片、网络安全与互联网</t>
+          <t>长安校区：南校区主校区；太白校区：北校区老校区；校史馆：讲述红色电子校史</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -813,39 +813,39 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>长安校区：南校区主校区；太白校区：北校区老校区；校史馆：讲述红色电子校史</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>西安电子科技大学</t>
+          <t>北京交通大学</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>交通运输、通信工程、电子信息工程、土木工程、计算机科学与技术、物流管理</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>交通运输、通信工程、电子信息工程、土木工程、计算机科学与技术、物流管理</t>
+          <t>轨道交通与铁路系统、通信与电子信息、金融与经济管理</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>轨道交通与铁路系统、通信与电子信息、金融与经济管理</t>
+          <t>思源楼：海淀校区标志建筑；詹天佑像：纪念中国铁路之父；威海校区：海滨新校区</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -901,39 +901,39 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>思源楼：海淀校区标志建筑；詹天佑像：纪念中国铁路之父；威海校区：海滨新校区</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>北京交通大学</t>
+          <t>华东理工大学</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>化学工程与工艺、应用化学、材料科学与工程、生物工程、制药工程、能源化学工程</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -945,17 +945,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>化学工程与工艺、应用化学、材料科学与工程、生物工程、制药工程、能源化学工程</t>
+          <t>化工与能源、新材料与制药、上海先进制造</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -967,17 +967,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>化工与能源、新材料与制药、上海先进制造</t>
+          <t>徐汇校区：梅陇路老校区；奉贤校区：海湾大学城校区；金山校区：新建校区</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -989,39 +989,39 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>徐汇校区：梅陇路老校区；奉贤校区：海湾大学城校区；金山校区：新建校区</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学</t>
+          <t>哈尔滨工程大学</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>船舶与海洋工程、核工程与核技术、水声工程、自动化、计算机科学与技术、信息与通信工程</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -1033,17 +1033,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>船舶与海洋工程、核工程与核技术、水声工程、自动化、计算机科学与技术、信息与通信工程</t>
+          <t>船舶与海洋装备、核电与能源、国防科研院所</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1055,17 +1055,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>知名校友</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>船舶与海洋装备、核电与能源、国防科研院所</t>
+          <t>杨德森、马远良（水声领域院士，百度百科列为杰出校友）</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核（学籍）</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>杨德森、马远良（水声领域院士，百度百科列为杰出校友）</t>
+          <t>哈军工旧址：大屋顶建筑群，国家级文保；军工广场：校园中心广场；青岛校区：海滨新校区</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>待核（学籍）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>哈军工旧址：大屋顶建筑群，国家级文保；军工广场：校园中心广场；青岛校区：海滨新校区</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨工程大学</t>
+          <t>郑州大学</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>临床医学、材料科学与工程、化学、土木工程、计算机科学与技术、法学</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -1143,17 +1143,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>临床医学、材料科学与工程、化学、土木工程、计算机科学与技术、法学</t>
+          <t>医疗卫生、党政机关与国企、电子信息与制造</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>医疗卫生、党政机关与国企、电子信息与制造</t>
+          <t>眉湖：主校区中心湖；主校区：高新区主校区；东校区：原郑州工业大学校区</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1187,39 +1187,39 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>眉湖：主校区中心湖；主校区：高新区主校区；东校区：原郑州工业大学校区</t>
+          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>郑州大学</t>
+          <t>华中农业大学</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>生物科学、园艺、动物医学、动物科学、农学、食品科学与工程</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -1231,17 +1231,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>生物科学、园艺、动物医学、动物科学、农学、食品科学与工程</t>
+          <t>农业与生命科学院所、食品与生物企业、党政机关与国企</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1253,17 +1253,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>农业与生命科学院所、食品与生物企业、党政机关与国企</t>
+          <t>狮子山：校园依山而建；南湖：校园南临南湖；试验田：田园风光的校园</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1275,39 +1275,39 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>狮子山：校园依山而建；南湖：校园南临南湖；试验田：田园风光的校园</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>华中农业大学</t>
+          <t>苏州大学</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>材料科学与工程、法学、临床医学、纺织工程、化学、软件工程</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1319,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>材料科学与工程、法学、临床医学、纺织工程、化学、软件工程</t>
+          <t>电子信息与制造、医疗卫生、长三角企业</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1341,17 +1341,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>电子信息与制造、医疗卫生、长三角企业</t>
+          <t>钟楼：东吴大学标志建筑；东吴大学旧址：全国重点文物保护单位；独墅湖校区：苏州工业园区校区</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1363,37 +1363,15 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>钟楼：东吴大学标志建筑；东吴大学旧址：全国重点文物保护单位；独墅湖校区：苏州工业园区校区</t>
+          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>苏州大学</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>待核2027年招生章程</t>
         </is>
@@ -5005,27 +4983,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>特色亮点（替代知名校友）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>孙聪等候选人学籍未核到可靠来源，海报暂显示“校友信息核实中”</t>
+          <t>国家重点实验室：机械结构力学及控制国家重点实验室；民航学院：培养民航飞行与运输人才；天目湖校区：溧阳新校区</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>校友信息核实中</t>
+          <t>国家重点实验室 机械结构力学及控制国家重点实验室；民航学院 培养民航飞行与运输人才；天目湖校区 溧阳新校区</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待补（等用户提供或核实后补）</t>
+          <t>学校官网、公开资料</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>较可靠，待核官网介绍（用户选B：无可靠校友时改放特色亮点）</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/字段表_211第一批.xlsx
+++ b/college-posters/data/字段表_211第一批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -505,68 +505,68 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>钢铁冶金与材料、智能制造与自动化、电子信息与互联网</t>
+          <t>主楼：学院路校区标志建筑；北科大体育馆：2008年奥运会比赛场馆；学院路校区：北京高校聚集区</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>南京理工大学</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>主楼：学院路校区标志建筑；北科大体育馆：2008年奥运会比赛场馆；学院路校区：北京高校聚集区</t>
+          <t>武器系统与工程、光电信息科学与工程、化学工程与工艺、自动化、计算机科学与技术、机械工程</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>北京科技大学</t>
+          <t>南京理工大学</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>水杉林：孝陵卫校区标志景观；二月兰：春季紫色花海；兵器博物馆：展示各类武器装备</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>南京理工大学</t>
+          <t>南京航空航天大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>武器系统与工程、光电信息科学与工程、化学工程与工艺、自动化、计算机科学与技术、机械工程</t>
+          <t>飞行器设计与工程、飞行器动力工程、交通运输、自动化、电子信息工程、计算机科学与技术</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -588,73 +588,73 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>南京理工大学</t>
+          <t>南京航空航天大学</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>国防军工科研院所、电子信息与智能制造、化工与新材料</t>
+          <t>明故宫校区：明故宫遗址旁老校区；将军路校区：江宁主校区；航空航天馆：展示各型飞机</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>南京理工大学</t>
+          <t>西安电子科技大学</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>水杉林：孝陵卫校区标志景观；二月兰：春季紫色花海；兵器博物馆：展示各类武器装备</t>
+          <t>通信工程、电子信息工程、网络空间安全、集成电路设计与集成系统、计算机科学与技术、人工智能</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>南京理工大学</t>
+          <t>西安电子科技大学</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>长安校区：南校区主校区；太白校区：北校区老校区；校史馆：讲述红色电子校史</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>南京航空航天大学</t>
+          <t>北京交通大学</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>飞行器设计与工程、飞行器动力工程、交通运输、自动化、电子信息工程、计算机科学与技术</t>
+          <t>交通运输、通信工程、电子信息工程、土木工程、计算机科学与技术、物流管理</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -676,73 +676,73 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>南京航空航天大学</t>
+          <t>北京交通大学</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>航空航天院所与企业、民航系统、电子信息与智能制造</t>
+          <t>思源楼：海淀校区标志建筑；詹天佑像：纪念中国铁路之父；威海校区：海滨新校区</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>南京航空航天大学</t>
+          <t>华东理工大学</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>明故宫校区：明故宫遗址旁老校区；将军路校区：江宁主校区；航空航天馆：展示各型飞机</t>
+          <t>化学工程与工艺、应用化学、材料科学与工程、生物工程、制药工程、能源化学工程</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>南京航空航天大学</t>
+          <t>华东理工大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>徐汇校区：梅陇路老校区；奉贤校区：海湾大学城校区；金山校区：新建校区</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>西安电子科技大学</t>
+          <t>哈尔滨工程大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>通信工程、电子信息工程、网络空间安全、集成电路设计与集成系统、计算机科学与技术、人工智能</t>
+          <t>船舶与海洋工程、核工程与核技术、水声工程、自动化、计算机科学与技术、信息与通信工程</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -764,73 +764,73 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>西安电子科技大学</t>
+          <t>哈尔滨工程大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>电子信息与通信、集成电路与芯片、网络安全与互联网</t>
+          <t>哈军工旧址：大屋顶建筑群，国家级文保；军工广场：校园中心广场；青岛校区：海滨新校区</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>西安电子科技大学</t>
+          <t>郑州大学</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>长安校区：南校区主校区；太白校区：北校区老校区；校史馆：讲述红色电子校史</t>
+          <t>临床医学、材料科学与工程、化学、土木工程、计算机科学与技术、法学</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>西安电子科技大学</t>
+          <t>郑州大学</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>眉湖：主校区中心湖；主校区：高新区主校区；东校区：原郑州工业大学校区</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>北京交通大学</t>
+          <t>华中农业大学</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>交通运输、通信工程、电子信息工程、土木工程、计算机科学与技术、物流管理</t>
+          <t>生物科学、园艺、动物医学、动物科学、农学、食品科学与工程</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -852,528 +852,66 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>北京交通大学</t>
+          <t>华中农业大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>轨道交通与铁路系统、通信与电子信息、金融与经济管理</t>
+          <t>狮子山：校园依山而建；南湖：校园南临南湖；试验田：田园风光的校园</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>北京交通大学</t>
+          <t>苏州大学</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>思源楼：海淀校区标志建筑；詹天佑像：纪念中国铁路之父；威海校区：海滨新校区</t>
+          <t>材料科学与工程、法学、临床医学、纺织工程、化学、软件工程</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>北京交通大学</t>
+          <t>苏州大学</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>钟楼：东吴大学标志建筑；东吴大学旧址：全国重点文物保护单位；独墅湖校区：苏州工业园区校区</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>华东理工大学</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>化学工程与工艺、应用化学、材料科学与工程、生物工程、制药工程、能源化学工程</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>华东理工大学</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>化工与能源、新材料与制药、上海先进制造</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>华东理工大学</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>徐汇校区：梅陇路老校区；奉贤校区：海湾大学城校区；金山校区：新建校区</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
           <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>华东理工大学</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>哈尔滨工程大学</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>船舶与海洋工程、核工程与核技术、水声工程、自动化、计算机科学与技术、信息与通信工程</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>哈尔滨工程大学</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>船舶与海洋装备、核电与能源、国防科研院所</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>哈尔滨工程大学</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>知名校友</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>杨德森、马远良（水声领域院士，百度百科列为杰出校友）</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>待核（学籍）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>哈尔滨工程大学</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>哈军工旧址：大屋顶建筑群，国家级文保；军工广场：校园中心广场；青岛校区：海滨新校区</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>哈尔滨工程大学</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>郑州大学</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>临床医学、材料科学与工程、化学、土木工程、计算机科学与技术、法学</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>郑州大学</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>医疗卫生、党政机关与国企、电子信息与制造</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>郑州大学</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>眉湖：主校区中心湖；主校区：高新区主校区；东校区：原郑州工业大学校区</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>郑州大学</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>华中农业大学</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>生物科学、园艺、动物医学、动物科学、农学、食品科学与工程</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>华中农业大学</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>农业与生命科学院所、食品与生物企业、党政机关与国企</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>华中农业大学</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>狮子山：校园依山而建；南湖：校园南临南湖；试验田：田园风光的校园</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>华中农业大学</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>苏州大学</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>材料科学与工程、法学、临床医学、纺织工程、化学、软件工程</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>苏州大学</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>电子信息与制造、医疗卫生、长三角企业</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>苏州大学</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>钟楼：东吴大学标志建筑；东吴大学旧址：全国重点文物保护单位；独墅湖校区：苏州工业园区校区</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>苏州大学</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
@@ -1937,9 +1475,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2062,12 +1600,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -2695,9 +2233,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2358,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -3453,9 +2991,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3116,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4211,9 +3749,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4336,12 +3874,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4969,9 +4507,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5094,12 +4632,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5727,9 +5265,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5390,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -6485,9 +6023,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6610,12 +6148,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7243,9 +6781,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -7368,12 +6906,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8001,9 +7539,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8015,27 +7553,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>特色亮点（替代知名校友）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>杨德森、马远良（水声领域院士，百度百科列为杰出校友）</t>
+          <t>马远良毕业于西北工业大学、杨德森学籍未核到，均撤下；改放水声工程（1953年创建的第一个声纳专业）、三海一核、双一流学科</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>杨德森 中国工程院院士；马远良 中国工程院院士</t>
+          <t>水声工程 我国第一个声纳专业，1953年创建；三海一核 船舶、海军、海洋、核能特色；船舶与海洋工程 国家双一流建设学科</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>百度百科</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待核（学籍）</t>
+          <t>学校官网、公开资料</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（已更正）</t>
         </is>
       </c>
     </row>
@@ -8126,12 +7664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8759,9 +8297,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8884,12 +8422,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/字段表_211第一批.xlsx
+++ b/college-posters/data/字段表_211第一批.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>长安校区：南校区主校区；太白校区：北校区老校区；校史馆：讲述红色电子校史</t>
+          <t>长安校区：南校区主校区；太白校区：北校区老校区；校史馆：讲述西电校史</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>长安校区：南校区主校区；太白校区：北校区老校区；校史馆：讲述红色电子校史</t>
+          <t>长安校区：南校区主校区；太白校区：北校区老校区；校史馆：讲述西电校史</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
